--- a/260603 New data set (reproducibility)/Overpotnital/Air BP/BOL/VC Polyol 1.5bp air OP BOL.xlsx
+++ b/260603 New data set (reproducibility)/Overpotnital/Air BP/BOL/VC Polyol 1.5bp air OP BOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\My Drive\KAIST MASc 2021\Laboratory Work\Protocol\overpotential calculation\For paper SI\260603 New data set (reproducibility)\Overpotnital\Air BP\BOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F649DB70-38CC-4BB8-B3F6-41F1C73076F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BC0479-213A-4CBB-91D6-9EAAF9725394}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23595" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
